--- a/data/trending_integrated_20260909_15.xlsx
+++ b/data/trending_integrated_20260909_15.xlsx
@@ -578,13 +578,13 @@
         <v>-1.06</v>
       </c>
       <c r="E2" t="n">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G2" t="n">
-        <v>1630</v>
+        <v>1668</v>
       </c>
       <c r="H2" t="n">
         <v>0.77</v>
@@ -610,7 +610,7 @@
         <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>29749128355</v>
+        <v>29766186935</v>
       </c>
       <c r="P2" t="n">
         <v>21500</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미 FDA 2A상 승인 및 병용요법 관련 연구 결과 공개 예고. 외인 매수세 유입으로 인한 기대감 형성.</t>
+          <t>미 FDA 2A상 승인 기대감 및 병용요법 연구 결과 공개 예정. 외국인 매수세 유입.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['FDA 2A상', '병용요법', '연구 결과']</t>
+          <t>['FDA 2A상', '병용요법', '외국인 매수']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F3" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G3" t="n">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H3" t="n">
         <v>0.36</v>
@@ -702,7 +702,7 @@
         <v>0.44</v>
       </c>
       <c r="O3" t="n">
-        <v>233282725825</v>
+        <v>233391187545</v>
       </c>
       <c r="P3" t="n">
         <v>20850</v>
@@ -768,7 +768,7 @@
         <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="H4" t="n">
         <v>2.46</v>
@@ -794,7 +794,7 @@
         <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>37954314615</v>
+        <v>37957849275</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13960</v>
+        <v>14160</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+18.20%</t>
+          <t>+19.90%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.22</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1532</v>
       </c>
       <c r="H5" t="n">
         <v>5.64</v>
@@ -886,7 +886,7 @@
         <v>5.42</v>
       </c>
       <c r="O5" t="n">
-        <v>487315522485</v>
+        <v>504360904950</v>
       </c>
       <c r="P5" t="n">
         <v>30200</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>하반기 주도주로서 원전 및 로봇 섹터 전망. 미국 및 사우디 등 해외 수주 기대감 반영. 13750원 및 22300원 등 단기 목표가 제시. 정부 정책 및 외국인 자본 유입 언급.</t>
+          <t>미국 원전주 강세 및 체코, 사우디 관련 이슈 언급. 하반기 주도주, 단기 급등 전망 제시하며 긍정적 논조 강화.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전', '로봇', '해외수주']</t>
+          <t>['원전', '체코', '사우디']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7200</v>
+        <v>7180</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+15.02%</t>
+          <t>+14.70%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F6" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G6" t="n">
-        <v>1301</v>
+        <v>1315</v>
       </c>
       <c r="H6" t="n">
         <v>7.4</v>
@@ -978,7 +978,7 @@
         <v>7.35</v>
       </c>
       <c r="O6" t="n">
-        <v>70629618770</v>
+        <v>71136651975</v>
       </c>
       <c r="P6" t="n">
         <v>21500</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14950</v>
+        <v>14900</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+9.12%</t>
+          <t>+8.76%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.39</v>
       </c>
       <c r="E7" t="n">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="F7" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G7" t="n">
-        <v>1484</v>
+        <v>1540</v>
       </c>
       <c r="H7" t="n">
         <v>1.55</v>
@@ -1070,7 +1070,7 @@
         <v>1.94</v>
       </c>
       <c r="O7" t="n">
-        <v>437313985410</v>
+        <v>442093417145</v>
       </c>
       <c r="P7" t="n">
         <v>31500</v>
@@ -1130,13 +1130,13 @@
         <v>0.03</v>
       </c>
       <c r="E8" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F8" t="n">
         <v>128</v>
       </c>
       <c r="G8" t="n">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="H8" t="n">
         <v>14.96</v>
@@ -1162,7 +1162,7 @@
         <v>14.93</v>
       </c>
       <c r="O8" t="n">
-        <v>165288875800</v>
+        <v>166382026200</v>
       </c>
       <c r="P8" t="n">
         <v>108900</v>
@@ -1207,83 +1207,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6840</v>
+        <v>2045</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+6.38%</t>
+          <t>+6.40%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.31</v>
+        <v>-0.1</v>
       </c>
       <c r="E9" t="n">
-        <v>355</v>
+        <v>126</v>
       </c>
       <c r="F9" t="n">
-        <v>158</v>
+        <v>48</v>
       </c>
       <c r="G9" t="n">
-        <v>558</v>
+        <v>310</v>
       </c>
       <c r="H9" t="n">
-        <v>16.71</v>
+        <v>0.51</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>6430</v>
+        <v>1922</v>
       </c>
       <c r="K9" t="n">
-        <v>6400</v>
+        <v>1920</v>
       </c>
       <c r="L9" t="n">
-        <v>7470</v>
+        <v>2165</v>
       </c>
       <c r="M9" t="n">
-        <v>6250</v>
+        <v>1862</v>
       </c>
       <c r="N9" t="n">
-        <v>16.4</v>
+        <v>0.61</v>
       </c>
       <c r="O9" t="n">
-        <v>100353110875</v>
+        <v>17990772384</v>
       </c>
       <c r="P9" t="n">
-        <v>13000</v>
+        <v>2930</v>
       </c>
       <c r="Q9" t="n">
-        <v>6030</v>
+        <v>910</v>
       </c>
       <c r="R9" t="n">
-        <v>-679000</v>
+        <v>154000</v>
       </c>
       <c r="S9" t="n">
-        <v>28000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>배당 관련 논의와 함께 주가 상승 및 하락에 대한 기대감 공존.</t>
+          <t>호남 반도체 클러스터 대장이라는 분석과 함께 텐버거 기대감 제시. 대주주 매도 공시, 물량 넘기기 등 부정적 언급도 공존.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['배당', '주가 상승', '공매']</t>
+          <t>['반도체', '텐버거', '대주주']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2035</v>
+        <v>6840</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+5.88%</t>
+          <t>+6.38%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.1</v>
+        <v>0.31</v>
       </c>
       <c r="E10" t="n">
-        <v>120</v>
+        <v>359</v>
       </c>
       <c r="F10" t="n">
-        <v>47</v>
+        <v>158</v>
       </c>
       <c r="G10" t="n">
-        <v>285</v>
+        <v>569</v>
       </c>
       <c r="H10" t="n">
-        <v>0.51</v>
+        <v>16.71</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1922</v>
+        <v>6430</v>
       </c>
       <c r="K10" t="n">
-        <v>1920</v>
+        <v>6400</v>
       </c>
       <c r="L10" t="n">
-        <v>2165</v>
+        <v>7470</v>
       </c>
       <c r="M10" t="n">
-        <v>1862</v>
+        <v>6250</v>
       </c>
       <c r="N10" t="n">
-        <v>0.61</v>
+        <v>16.4</v>
       </c>
       <c r="O10" t="n">
-        <v>17571997184</v>
+        <v>100921006795</v>
       </c>
       <c r="P10" t="n">
-        <v>2930</v>
+        <v>13000</v>
       </c>
       <c r="Q10" t="n">
-        <v>910</v>
+        <v>6030</v>
       </c>
       <c r="R10" t="n">
-        <v>154000</v>
+        <v>-679000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>반도체 클러스터 관련 논의 및 주포 동향 주시, 주가 상승 전망.</t>
+          <t>배당금 관련 긍정적 언급과 함께 일부 하락 예측 존재. 거래량 증가 및 손바뀜 추정으로 상승 기대감 나타남.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['반도체 클러스터', '주포', '텐버거']</t>
+          <t>['배당금', '거래량', '손바뀜']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,169 +1384,169 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3800</v>
+        <v>2260</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+4.40%</t>
+          <t>+4.63%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2.74</v>
+        <v>-0.23</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
       <c r="H11" t="n">
-        <v>3.19</v>
+        <v>5.26</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>3640</v>
+        <v>2160</v>
       </c>
       <c r="K11" t="n">
-        <v>3750</v>
+        <v>2200</v>
       </c>
       <c r="L11" t="n">
-        <v>4460</v>
+        <v>2705</v>
       </c>
       <c r="M11" t="n">
-        <v>3680</v>
+        <v>2130</v>
       </c>
       <c r="N11" t="n">
-        <v>0.45</v>
+        <v>5.49</v>
       </c>
       <c r="O11" t="n">
-        <v>274896197449</v>
+        <v>46160448335</v>
       </c>
       <c r="P11" t="n">
-        <v>8100</v>
+        <v>2705</v>
       </c>
       <c r="Q11" t="n">
-        <v>592</v>
+        <v>1418</v>
       </c>
       <c r="R11" t="n">
-        <v>-731000</v>
+        <v>22000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 광통신 폭등 관련, 6G 기반, 국책사업 선정 기대.</t>
+          <t>기타법인 장내매수 및 새로운 대주주에 대한 기대감 존재. 일부는 하한가 및 음봉을 예측하며 부정적인 전망도 제시.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', '6G']</t>
+          <t>['기타법인', '대주주', '음봉']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1859000</v>
+        <v>3805</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+3.68%</t>
+          <t>+4.53%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.03</v>
+        <v>2.74</v>
       </c>
       <c r="E12" t="n">
-        <v>791</v>
+        <v>237</v>
       </c>
       <c r="F12" t="n">
-        <v>438</v>
+        <v>128</v>
       </c>
       <c r="G12" t="n">
-        <v>1846</v>
+        <v>554</v>
       </c>
       <c r="H12" t="n">
-        <v>50.66</v>
+        <v>3.19</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1793000</v>
+        <v>3640</v>
       </c>
       <c r="K12" t="n">
-        <v>1795000</v>
+        <v>3750</v>
       </c>
       <c r="L12" t="n">
-        <v>1883000</v>
+        <v>4460</v>
       </c>
       <c r="M12" t="n">
-        <v>1795000</v>
+        <v>3680</v>
       </c>
       <c r="N12" t="n">
-        <v>50.63</v>
+        <v>0.45</v>
       </c>
       <c r="O12" t="n">
-        <v>5776700759500</v>
+        <v>276093833628</v>
       </c>
       <c r="P12" t="n">
-        <v>2987000</v>
+        <v>8100</v>
       </c>
       <c r="Q12" t="n">
-        <v>277000</v>
+        <v>592</v>
       </c>
       <c r="R12" t="n">
-        <v>180000</v>
+        <v>-731000</v>
       </c>
       <c r="S12" t="n">
-        <v>151000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>외인 매수세 유입 및 상승 추세 전환 신호 포착, 긍정적 전망.</t>
+          <t>미국 광통신 섹터 강세 및 글로벌 회사 대량 공급 뉴스 기반으로 긍정적 전망 제시. 투경 우려와 함께 1만 전자, 6천원 목표가 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['외인 매수', '상승 추세', '호재']</t>
+          <t>['광통신', '글로벌 공급', '투경']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30750</v>
+        <v>1857000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.36%</t>
+          <t>+3.57%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="E13" t="n">
-        <v>714</v>
+        <v>792</v>
       </c>
       <c r="F13" t="n">
-        <v>252</v>
+        <v>427</v>
       </c>
       <c r="G13" t="n">
-        <v>1032</v>
+        <v>1992</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31</v>
+        <v>50.66</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>29750</v>
+        <v>1793000</v>
       </c>
       <c r="K13" t="n">
-        <v>31600</v>
+        <v>1795000</v>
       </c>
       <c r="L13" t="n">
-        <v>34200</v>
+        <v>1883000</v>
       </c>
       <c r="M13" t="n">
-        <v>28300</v>
+        <v>1795000</v>
       </c>
       <c r="N13" t="n">
-        <v>0.23</v>
+        <v>50.63</v>
       </c>
       <c r="O13" t="n">
-        <v>522764760150</v>
+        <v>5874294887500</v>
       </c>
       <c r="P13" t="n">
-        <v>39350</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>8200</v>
+        <v>277000</v>
       </c>
       <c r="R13" t="n">
-        <v>-1000</v>
+        <v>180000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>151000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>혈압계 관련 뉴스 및 유럽 진출 소식, 주가 반등 기대감.</t>
+          <t>상승 추세 전환 신호 및 외인/기관의 긍정적 수급 포착. 악성 매물 소화 및 우상향 표준이라는 분석 제시. 일부 2시 이후 하락 예측 존재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['혈압계', '유럽 진출', '최저점']</t>
+          <t>['상승 추세', '수급', '악성매물']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>91800</v>
+        <v>7900</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+2.57%</t>
+          <t>+2.86%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.02</v>
+        <v>1.4</v>
       </c>
       <c r="E14" t="n">
-        <v>355</v>
+        <v>143</v>
       </c>
       <c r="F14" t="n">
-        <v>225</v>
+        <v>86</v>
       </c>
       <c r="G14" t="n">
-        <v>1739</v>
+        <v>363</v>
       </c>
       <c r="H14" t="n">
-        <v>23.61</v>
+        <v>1.81</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>89500</v>
+        <v>7680</v>
       </c>
       <c r="K14" t="n">
-        <v>92000</v>
+        <v>7780</v>
       </c>
       <c r="L14" t="n">
-        <v>94400</v>
+        <v>9000</v>
       </c>
       <c r="M14" t="n">
-        <v>91100</v>
+        <v>7690</v>
       </c>
       <c r="N14" t="n">
-        <v>23.63</v>
+        <v>0.41</v>
       </c>
       <c r="O14" t="n">
-        <v>319193723450</v>
+        <v>120266040840</v>
       </c>
       <c r="P14" t="n">
-        <v>139200</v>
+        <v>10300</v>
       </c>
       <c r="Q14" t="n">
-        <v>57000</v>
+        <v>952</v>
       </c>
       <c r="R14" t="n">
-        <v>123000</v>
+        <v>-211000</v>
       </c>
       <c r="S14" t="n">
-        <v>96000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 원전주 급등 및 SMR 관련 긍정적 전망. 한-프랑스 정상회담 원자력 협력 기대감 반영. 하반기 주도주 가능성 및 대미 투자 수혜 언급.</t>
+          <t>강력한 지지선 및 신고가 돌파 기대감 존재. 일부는 하락 및 숏커버링 가능성을 언급하며 관망세.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '한-프랑스']</t>
+          <t>['지지선', '돌파', '숏커버링']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7860</v>
+        <v>30550</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+2.34%</t>
+          <t>+2.69%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.4</v>
+        <v>0.08</v>
       </c>
       <c r="E15" t="n">
-        <v>147</v>
+        <v>725</v>
       </c>
       <c r="F15" t="n">
-        <v>85</v>
+        <v>253</v>
       </c>
       <c r="G15" t="n">
-        <v>390</v>
+        <v>1046</v>
       </c>
       <c r="H15" t="n">
-        <v>1.81</v>
+        <v>0.31</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>7680</v>
+        <v>29750</v>
       </c>
       <c r="K15" t="n">
-        <v>7780</v>
+        <v>31600</v>
       </c>
       <c r="L15" t="n">
-        <v>9000</v>
+        <v>34200</v>
       </c>
       <c r="M15" t="n">
-        <v>7690</v>
+        <v>28300</v>
       </c>
       <c r="N15" t="n">
-        <v>0.41</v>
+        <v>0.23</v>
       </c>
       <c r="O15" t="n">
-        <v>119236391540</v>
+        <v>529460328575</v>
       </c>
       <c r="P15" t="n">
-        <v>10300</v>
+        <v>39350</v>
       </c>
       <c r="Q15" t="n">
-        <v>952</v>
+        <v>8200</v>
       </c>
       <c r="R15" t="n">
-        <v>-211000</v>
+        <v>-1000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>레미콘 파업 시작 및 대장주로서의 강세 기대. 하지만 전반적인 상승 동력은 약함.</t>
+          <t>혈압계 관련 뉴스 및 유럽 진출 소식, 주가 반등 기대감.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['레미콘', '대장주', '파업']</t>
+          <t>['혈압계', '유럽 진출', '최저점']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2185</v>
+        <v>91700</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+1.16%</t>
+          <t>+2.46%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.23</v>
+        <v>-0.02</v>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>358</v>
       </c>
       <c r="F16" t="n">
-        <v>84</v>
+        <v>227</v>
       </c>
       <c r="G16" t="n">
-        <v>375</v>
+        <v>1754</v>
       </c>
       <c r="H16" t="n">
-        <v>5.26</v>
+        <v>23.61</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>2160</v>
+        <v>89500</v>
       </c>
       <c r="K16" t="n">
-        <v>2200</v>
+        <v>92000</v>
       </c>
       <c r="L16" t="n">
-        <v>2705</v>
+        <v>94400</v>
       </c>
       <c r="M16" t="n">
-        <v>2130</v>
+        <v>91100</v>
       </c>
       <c r="N16" t="n">
-        <v>5.49</v>
+        <v>23.63</v>
       </c>
       <c r="O16" t="n">
-        <v>44640050294</v>
+        <v>325255660850</v>
       </c>
       <c r="P16" t="n">
-        <v>2705</v>
+        <v>139200</v>
       </c>
       <c r="Q16" t="n">
-        <v>1418</v>
+        <v>57000</v>
       </c>
       <c r="R16" t="n">
-        <v>22000</v>
+        <v>123000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>96000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>지분 싸움 및 신규 대주주 관련 논의, 단기 목표가 언급.</t>
+          <t>미국 원전주 급등 및 SMR 관련 긍정적 전망. 한-프랑스 정상회담 원자력 협력 기대감 반영. 하반기 주도주 가능성 및 대미 투자 수혜 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['지분 싸움', '신규 대주주', '단기 목표가']</t>
+          <t>['원전', 'SMR', '한-프랑스']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12050</v>
+        <v>12120</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>191</v>
       </c>
       <c r="F17" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G17" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
         <v>2.16</v>
       </c>
       <c r="O17" t="n">
-        <v>48540091605</v>
+        <v>49177428615</v>
       </c>
       <c r="P17" t="n">
         <v>36200</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>국제 유가 급등 및 지정학적 이슈에도 주가 부진, 투자자들의 불만.</t>
+          <t>국제 유가 급등 및 이란 관련 이슈로 인한 상승 기대감 있으나, 주가는 반응이 없고 오히려 하락했다는 분석 제시.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['국제 유가', '지정학적 이슈', '주가 부진']</t>
+          <t>['국제유가', '이란', '주가 반응']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>270500</v>
+        <v>8970</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.06</v>
+        <v>-0.36</v>
       </c>
       <c r="E18" t="n">
-        <v>763</v>
+        <v>121</v>
       </c>
       <c r="F18" t="n">
-        <v>476</v>
+        <v>68</v>
       </c>
       <c r="G18" t="n">
-        <v>1711</v>
+        <v>524</v>
       </c>
       <c r="H18" t="n">
-        <v>46.85</v>
+        <v>27.69</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>269500</v>
+        <v>8940</v>
       </c>
       <c r="K18" t="n">
-        <v>269500</v>
+        <v>8940</v>
       </c>
       <c r="L18" t="n">
-        <v>275000</v>
+        <v>9070</v>
       </c>
       <c r="M18" t="n">
-        <v>267500</v>
+        <v>8710</v>
       </c>
       <c r="N18" t="n">
-        <v>46.79</v>
+        <v>28.05</v>
       </c>
       <c r="O18" t="n">
-        <v>3879752757000</v>
+        <v>34206964330</v>
       </c>
       <c r="P18" t="n">
-        <v>374500</v>
+        <v>17950</v>
       </c>
       <c r="Q18" t="n">
-        <v>70000</v>
+        <v>8120</v>
       </c>
       <c r="R18" t="n">
-        <v>-1876000</v>
+        <v>-309000</v>
       </c>
       <c r="S18" t="n">
-        <v>784000</v>
+        <v>7000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>노조, 경영진 관련 부정적 언급 및 주가 부진에 대한 불만.</t>
+          <t>기업 실적 및 성장성에 대한 부정적 전망, 투자 비판.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['노조', '경영진', '주가 부진']</t>
+          <t>['실적', '성장성', '투자 비판']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8970</v>
+        <v>270000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.36</v>
+        <v>0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>120</v>
+        <v>787</v>
       </c>
       <c r="F19" t="n">
-        <v>68</v>
+        <v>489</v>
       </c>
       <c r="G19" t="n">
-        <v>516</v>
+        <v>1758</v>
       </c>
       <c r="H19" t="n">
-        <v>27.69</v>
+        <v>46.85</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>8940</v>
+        <v>269500</v>
       </c>
       <c r="K19" t="n">
-        <v>8940</v>
+        <v>269500</v>
       </c>
       <c r="L19" t="n">
-        <v>9070</v>
+        <v>275000</v>
       </c>
       <c r="M19" t="n">
-        <v>8710</v>
+        <v>267500</v>
       </c>
       <c r="N19" t="n">
-        <v>28.05</v>
+        <v>46.79</v>
       </c>
       <c r="O19" t="n">
-        <v>33176217140</v>
+        <v>3951124796250</v>
       </c>
       <c r="P19" t="n">
-        <v>17950</v>
+        <v>374500</v>
       </c>
       <c r="Q19" t="n">
-        <v>8120</v>
+        <v>70000</v>
       </c>
       <c r="R19" t="n">
-        <v>-309000</v>
+        <v>-1876000</v>
       </c>
       <c r="S19" t="n">
-        <v>7000</v>
+        <v>784000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>기업 실적 및 성장성에 대한 부정적 전망, 투자 비판.</t>
+          <t>노조, 이재용 관련 이슈 및 외인 매도세에 대한 부정적 언급과 함께 영업이익 전세계 1위라는 팩트 제시. 주가 하락 및 희망 없는 전망 다수.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['실적', '성장성', '투자 비판']</t>
+          <t>['노조', '외인 매도', '영업이익']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,222 +2212,222 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>33700</v>
+        <v>3870</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.1</v>
+        <v>0.52</v>
       </c>
       <c r="E20" t="n">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="F20" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="G20" t="n">
-        <v>322</v>
+        <v>201</v>
       </c>
       <c r="H20" t="n">
-        <v>52.56</v>
+        <v>2.08</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>34100</v>
+        <v>3890</v>
       </c>
       <c r="K20" t="n">
-        <v>34450</v>
+        <v>3890</v>
       </c>
       <c r="L20" t="n">
-        <v>35325</v>
+        <v>4115</v>
       </c>
       <c r="M20" t="n">
-        <v>33550</v>
+        <v>3700</v>
       </c>
       <c r="N20" t="n">
-        <v>21.01</v>
+        <v>1.56</v>
       </c>
       <c r="O20" t="n">
-        <v>85214685575</v>
+        <v>70042091952</v>
       </c>
       <c r="P20" t="n">
-        <v>69500</v>
+        <v>4335</v>
       </c>
       <c r="Q20" t="n">
-        <v>30400</v>
+        <v>1246</v>
       </c>
       <c r="R20" t="n">
-        <v>-80000</v>
+        <v>-599000</v>
       </c>
       <c r="S20" t="n">
-        <v>58000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 원전 협력, 공매도 이슈, SMP 급락 우려.</t>
+          <t>탈모 관련주로 언급되나 구체적인 재료 및 뉴스 부재, 하락 추세 및 조정 국면.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['원전', '공매도']</t>
+          <t>['탈모주', '하락']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3800</v>
+        <v>33750</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.52</v>
+        <v>0.1</v>
       </c>
       <c r="E21" t="n">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="F21" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G21" t="n">
-        <v>197</v>
+        <v>324</v>
       </c>
       <c r="H21" t="n">
-        <v>2.08</v>
+        <v>52.55</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>3890</v>
+        <v>34100</v>
       </c>
       <c r="K21" t="n">
-        <v>3890</v>
+        <v>34450</v>
       </c>
       <c r="L21" t="n">
-        <v>4115</v>
+        <v>35325</v>
       </c>
       <c r="M21" t="n">
-        <v>3700</v>
+        <v>33550</v>
       </c>
       <c r="N21" t="n">
-        <v>1.56</v>
+        <v>21.01</v>
       </c>
       <c r="O21" t="n">
-        <v>67606736408</v>
+        <v>86575259200</v>
       </c>
       <c r="P21" t="n">
-        <v>4335</v>
+        <v>69500</v>
       </c>
       <c r="Q21" t="n">
-        <v>1246</v>
+        <v>30400</v>
       </c>
       <c r="R21" t="n">
-        <v>-599000</v>
+        <v>-80000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>58000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>탈모 관련주로 언급되나 구체적인 재료 및 뉴스 부재, 하락 추세 및 조정 국면.</t>
+          <t>미국 원전 협력 및 발전 5사 통합, 25조 선납매 관련 긍정적 이슈 언급. 공매도 세력 및 20년째 주주 피해 상황으로 부정적 전망도 제시.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['탈모주', '하락']</t>
+          <t>['원전', '발전 5사 통합', '공매도']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>015760</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19480</v>
+        <v>10200</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.45%</t>
+          <t>-2.30%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="E22" t="n">
-        <v>249</v>
+        <v>107</v>
       </c>
       <c r="F22" t="n">
-        <v>128</v>
+        <v>72</v>
       </c>
       <c r="G22" t="n">
-        <v>766</v>
+        <v>257</v>
       </c>
       <c r="H22" t="n">
-        <v>10.85</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,91 +2435,91 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>19970</v>
+        <v>10440</v>
       </c>
       <c r="K22" t="n">
-        <v>20250</v>
+        <v>10180</v>
       </c>
       <c r="L22" t="n">
-        <v>21300</v>
+        <v>11340</v>
       </c>
       <c r="M22" t="n">
-        <v>19350</v>
+        <v>9980</v>
       </c>
       <c r="N22" t="n">
-        <v>10.47</v>
+        <v>0.62</v>
       </c>
       <c r="O22" t="n">
-        <v>284975878165</v>
+        <v>149740010280</v>
       </c>
       <c r="P22" t="n">
-        <v>40350</v>
+        <v>15960</v>
       </c>
       <c r="Q22" t="n">
-        <v>3320</v>
+        <v>3500</v>
       </c>
       <c r="R22" t="n">
-        <v>-1107000</v>
+        <v>-50000</v>
       </c>
       <c r="S22" t="n">
-        <v>-209000</v>
+        <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>원전 관련 호재 속 계약 체결 공시 확인, 일부 투자자 기대감.</t>
+          <t>미증시 제약바이오와는 다른 움직임, 탈모주 관련 기대감 있으나 구체적인 재료 및 공시 부재.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['원전', '공시', '계약체결']</t>
+          <t>['탈모주', '재료']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10130</v>
+        <v>19450</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.97%</t>
+          <t>-2.60%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="E23" t="n">
-        <v>104</v>
+        <v>254</v>
       </c>
       <c r="F23" t="n">
-        <v>71</v>
+        <v>130</v>
       </c>
       <c r="G23" t="n">
-        <v>249</v>
+        <v>777</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9399999999999999</v>
+        <v>10.85</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,60 +2527,60 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>10440</v>
+        <v>19970</v>
       </c>
       <c r="K23" t="n">
-        <v>10180</v>
+        <v>20250</v>
       </c>
       <c r="L23" t="n">
-        <v>11340</v>
+        <v>21300</v>
       </c>
       <c r="M23" t="n">
-        <v>9980</v>
+        <v>19350</v>
       </c>
       <c r="N23" t="n">
-        <v>0.62</v>
+        <v>10.47</v>
       </c>
       <c r="O23" t="n">
-        <v>148040577390</v>
+        <v>289449585835</v>
       </c>
       <c r="P23" t="n">
-        <v>15960</v>
+        <v>40350</v>
       </c>
       <c r="Q23" t="n">
-        <v>3500</v>
+        <v>3320</v>
       </c>
       <c r="R23" t="n">
-        <v>-50000</v>
+        <v>-1107000</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>-209000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>미증시 제약바이오와는 다른 움직임, 탈모주 관련 기대감 있으나 구체적인 재료 및 공시 부재.</t>
+          <t>원전 관련 호재 속 계약 체결 공시 확인, 일부 투자자 기대감.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['탈모주', '재료']</t>
+          <t>['원전', '공시', '계약체결']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>047040</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260909_15.xlsx
+++ b/data/trending_integrated_20260909_15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z23"/>
+  <dimension ref="A1:Z24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-1.06</v>
       </c>
       <c r="E2" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G2" t="n">
-        <v>1668</v>
+        <v>1683</v>
       </c>
       <c r="H2" t="n">
         <v>0.77</v>
@@ -610,7 +610,7 @@
         <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>29766186935</v>
+        <v>29784514335</v>
       </c>
       <c r="P2" t="n">
         <v>21500</v>
@@ -670,13 +670,13 @@
         <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F3" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G3" t="n">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="H3" t="n">
         <v>0.36</v>
@@ -702,7 +702,7 @@
         <v>0.44</v>
       </c>
       <c r="O3" t="n">
-        <v>233391187545</v>
+        <v>233465315215</v>
       </c>
       <c r="P3" t="n">
         <v>20850</v>
@@ -762,13 +762,13 @@
         <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F4" t="n">
         <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="H4" t="n">
         <v>2.46</v>
@@ -794,7 +794,7 @@
         <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>37957849275</v>
+        <v>37978952115</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14160</v>
+        <v>14290</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+19.90%</t>
+          <t>+21.00%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.22</v>
       </c>
       <c r="E5" t="n">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="F5" t="n">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="G5" t="n">
-        <v>1532</v>
+        <v>1575</v>
       </c>
       <c r="H5" t="n">
         <v>5.64</v>
@@ -886,7 +886,7 @@
         <v>5.42</v>
       </c>
       <c r="O5" t="n">
-        <v>504360904950</v>
+        <v>522857428495</v>
       </c>
       <c r="P5" t="n">
         <v>30200</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7180</v>
+        <v>7150</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+14.70%</t>
+          <t>+14.22%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F6" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G6" t="n">
-        <v>1315</v>
+        <v>1339</v>
       </c>
       <c r="H6" t="n">
         <v>7.4</v>
@@ -978,7 +978,7 @@
         <v>7.35</v>
       </c>
       <c r="O6" t="n">
-        <v>71136651975</v>
+        <v>71771967855</v>
       </c>
       <c r="P6" t="n">
         <v>21500</v>
@@ -1023,70 +1023,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14900</v>
+        <v>53900</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+8.76%</t>
+          <t>+9.44%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.39</v>
+        <v>0.03</v>
       </c>
       <c r="E7" t="n">
-        <v>279</v>
+        <v>175</v>
       </c>
       <c r="F7" t="n">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="G7" t="n">
-        <v>1540</v>
+        <v>660</v>
       </c>
       <c r="H7" t="n">
-        <v>1.55</v>
+        <v>14.96</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>13700</v>
+        <v>49250</v>
       </c>
       <c r="K7" t="n">
-        <v>14260</v>
+        <v>53500</v>
       </c>
       <c r="L7" t="n">
-        <v>15860</v>
+        <v>59000</v>
       </c>
       <c r="M7" t="n">
-        <v>14210</v>
+        <v>51600</v>
       </c>
       <c r="N7" t="n">
-        <v>1.94</v>
+        <v>14.93</v>
       </c>
       <c r="O7" t="n">
-        <v>442093417145</v>
+        <v>167660719050</v>
       </c>
       <c r="P7" t="n">
-        <v>31500</v>
+        <v>108900</v>
       </c>
       <c r="Q7" t="n">
-        <v>1252</v>
+        <v>18230</v>
       </c>
       <c r="R7" t="n">
-        <v>590000</v>
+        <v>-215000</v>
       </c>
       <c r="S7" t="n">
-        <v>20000</v>
+        <v>154000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>단기 박스권 돌파 및 불기둥 형성, 2만 목표 상향 기대감.</t>
+          <t>대규모 수주 및 2분기 영업이익 흑자 전환 기대감. 목표가 상향 논의 활발.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['불기둥', '박스권돌파', '우상향']</t>
+          <t>['수주', '영업이익', '목표가']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,77 +1108,77 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>53500</v>
+        <v>14960</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+8.63%</t>
+          <t>+9.20%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.03</v>
+        <v>-0.39</v>
       </c>
       <c r="E8" t="n">
-        <v>173</v>
+        <v>282</v>
       </c>
       <c r="F8" t="n">
-        <v>128</v>
+        <v>169</v>
       </c>
       <c r="G8" t="n">
-        <v>627</v>
+        <v>1565</v>
       </c>
       <c r="H8" t="n">
-        <v>14.96</v>
+        <v>1.55</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>49250</v>
+        <v>13700</v>
       </c>
       <c r="K8" t="n">
-        <v>53500</v>
+        <v>14260</v>
       </c>
       <c r="L8" t="n">
-        <v>59000</v>
+        <v>15860</v>
       </c>
       <c r="M8" t="n">
-        <v>51600</v>
+        <v>14210</v>
       </c>
       <c r="N8" t="n">
-        <v>14.93</v>
+        <v>1.94</v>
       </c>
       <c r="O8" t="n">
-        <v>166382026200</v>
+        <v>447240616025</v>
       </c>
       <c r="P8" t="n">
-        <v>108900</v>
+        <v>31500</v>
       </c>
       <c r="Q8" t="n">
-        <v>18230</v>
+        <v>1252</v>
       </c>
       <c r="R8" t="n">
-        <v>-215000</v>
+        <v>590000</v>
       </c>
       <c r="S8" t="n">
-        <v>154000</v>
+        <v>20000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>대규모 수주 및 2분기 영업이익 흑자 전환 기대감. 목표가 상향 논의 활발.</t>
+          <t>빛과전자 수급 흡수 및 개인 매도세 속 상승 기대. 단기 박스권 돌파 및 우상향 추세.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['수주', '영업이익', '목표가']</t>
+          <t>['수급', '단기 박스권', '우상향']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2045</v>
+        <v>2090</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+6.40%</t>
+          <t>+8.74%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>126</v>
       </c>
       <c r="F9" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G9" t="n">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="H9" t="n">
         <v>0.51</v>
@@ -1254,7 +1254,7 @@
         <v>0.61</v>
       </c>
       <c r="O9" t="n">
-        <v>17990772384</v>
+        <v>18309827760</v>
       </c>
       <c r="P9" t="n">
         <v>2930</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>호남 반도체 클러스터 대장이라는 분석과 함께 텐버거 기대감 제시. 대주주 매도 공시, 물량 넘기기 등 부정적 언급도 공존.</t>
+          <t>반도체 클러스터 대장주 언급 및 텐버거 찌라시. 대주주 매도 공시 및 물량 넘기기 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['반도체', '텐버거', '대주주']</t>
+          <t>['반도체 클러스터', '텐버거', '대주주 매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6840</v>
+        <v>6850</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+6.38%</t>
+          <t>+6.53%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.31</v>
       </c>
       <c r="E10" t="n">
-        <v>359</v>
+        <v>299</v>
       </c>
       <c r="F10" t="n">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="G10" t="n">
-        <v>569</v>
+        <v>528</v>
       </c>
       <c r="H10" t="n">
         <v>16.71</v>
@@ -1346,7 +1346,7 @@
         <v>16.4</v>
       </c>
       <c r="O10" t="n">
-        <v>100921006795</v>
+        <v>102089843410</v>
       </c>
       <c r="P10" t="n">
         <v>13000</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>배당금 관련 긍정적 언급과 함께 일부 하락 예측 존재. 거래량 증가 및 손바뀜 추정으로 상승 기대감 나타남.</t>
+          <t>배당금 대비 낮은 주가 및 시총 관련 논의. 거래량 증가와 함께 일부 상승 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['배당금', '거래량', '손바뀜']</t>
+          <t>['배당금', '시가총액', '거래량']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,70 +1391,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2260</v>
+        <v>8340</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+4.63%</t>
+          <t>+5.97%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.23</v>
+        <v>0.46</v>
       </c>
       <c r="E11" t="n">
-        <v>180</v>
+        <v>129</v>
       </c>
       <c r="F11" t="n">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="G11" t="n">
-        <v>347</v>
+        <v>175</v>
       </c>
       <c r="H11" t="n">
-        <v>5.26</v>
+        <v>39.3</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2160</v>
+        <v>7870</v>
       </c>
       <c r="K11" t="n">
-        <v>2200</v>
+        <v>7950</v>
       </c>
       <c r="L11" t="n">
-        <v>2705</v>
+        <v>8350</v>
       </c>
       <c r="M11" t="n">
-        <v>2130</v>
+        <v>7480</v>
       </c>
       <c r="N11" t="n">
-        <v>5.49</v>
+        <v>38.84</v>
       </c>
       <c r="O11" t="n">
-        <v>46160448335</v>
+        <v>42363747010</v>
       </c>
       <c r="P11" t="n">
-        <v>2705</v>
+        <v>19150</v>
       </c>
       <c r="Q11" t="n">
-        <v>1418</v>
+        <v>3445</v>
       </c>
       <c r="R11" t="n">
-        <v>22000</v>
+        <v>-169000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-393000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>기타법인 장내매수 및 새로운 대주주에 대한 기대감 존재. 일부는 하한가 및 음봉을 예측하며 부정적인 전망도 제시.</t>
+          <t>물량 터는 중이라는 의견과 함께 급락. 상패 직전 우려 및 유증 재료 소멸.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['기타법인', '대주주', '음봉']</t>
+          <t>['물량 터는 중', '급락', '유증 재료 소멸']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>033790</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3805</v>
+        <v>2260</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+4.53%</t>
+          <t>+4.63%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2.74</v>
+        <v>-0.23</v>
       </c>
       <c r="E12" t="n">
-        <v>237</v>
+        <v>200</v>
       </c>
       <c r="F12" t="n">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="G12" t="n">
-        <v>554</v>
+        <v>397</v>
       </c>
       <c r="H12" t="n">
-        <v>3.19</v>
+        <v>5.26</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3640</v>
+        <v>2160</v>
       </c>
       <c r="K12" t="n">
-        <v>3750</v>
+        <v>2200</v>
       </c>
       <c r="L12" t="n">
-        <v>4460</v>
+        <v>2705</v>
       </c>
       <c r="M12" t="n">
-        <v>3680</v>
+        <v>2130</v>
       </c>
       <c r="N12" t="n">
-        <v>0.45</v>
+        <v>5.49</v>
       </c>
       <c r="O12" t="n">
-        <v>276093833628</v>
+        <v>47851656010</v>
       </c>
       <c r="P12" t="n">
-        <v>8100</v>
+        <v>2705</v>
       </c>
       <c r="Q12" t="n">
-        <v>592</v>
+        <v>1418</v>
       </c>
       <c r="R12" t="n">
-        <v>-731000</v>
+        <v>22000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 광통신 섹터 강세 및 글로벌 회사 대량 공급 뉴스 기반으로 긍정적 전망 제시. 투경 우려와 함께 1만 전자, 6천원 목표가 언급.</t>
+          <t>지분 싸움 및 기타법인 장내매수 포착. 단기 과열 우려 속 변동성 확대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', '글로벌 공급', '투경']</t>
+          <t>['지분 싸움', '장내매수', '단기 과열']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,77 +1568,77 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1857000</v>
+        <v>3805</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.57%</t>
+          <t>+4.53%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.03</v>
+        <v>2.74</v>
       </c>
       <c r="E13" t="n">
-        <v>792</v>
+        <v>245</v>
       </c>
       <c r="F13" t="n">
-        <v>427</v>
+        <v>131</v>
       </c>
       <c r="G13" t="n">
-        <v>1992</v>
+        <v>562</v>
       </c>
       <c r="H13" t="n">
-        <v>50.66</v>
+        <v>3.19</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1793000</v>
+        <v>3640</v>
       </c>
       <c r="K13" t="n">
-        <v>1795000</v>
+        <v>3750</v>
       </c>
       <c r="L13" t="n">
-        <v>1883000</v>
+        <v>4460</v>
       </c>
       <c r="M13" t="n">
-        <v>1795000</v>
+        <v>3680</v>
       </c>
       <c r="N13" t="n">
-        <v>50.63</v>
+        <v>0.45</v>
       </c>
       <c r="O13" t="n">
-        <v>5874294887500</v>
+        <v>277930731752</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>8100</v>
       </c>
       <c r="Q13" t="n">
-        <v>277000</v>
+        <v>592</v>
       </c>
       <c r="R13" t="n">
-        <v>180000</v>
+        <v>-731000</v>
       </c>
       <c r="S13" t="n">
-        <v>151000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>상승 추세 전환 신호 및 외인/기관의 긍정적 수급 포착. 악성 매물 소화 및 우상향 표준이라는 분석 제시. 일부 2시 이후 하락 예측 존재.</t>
+          <t>미국 광통신 섹터 급등에 따른 기대감. 글로벌 회사 대량 공급 뉴스 및 6G 기반 재료.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['상승 추세', '수급', '악성매물']</t>
+          <t>['광통신', '글로벌 공급', '6G']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7900</v>
+        <v>1858000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+2.86%</t>
+          <t>+3.63%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.4</v>
+        <v>0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>143</v>
+        <v>793</v>
       </c>
       <c r="F14" t="n">
-        <v>86</v>
+        <v>423</v>
       </c>
       <c r="G14" t="n">
-        <v>363</v>
+        <v>2124</v>
       </c>
       <c r="H14" t="n">
-        <v>1.81</v>
+        <v>50.66</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>7680</v>
+        <v>1793000</v>
       </c>
       <c r="K14" t="n">
-        <v>7780</v>
+        <v>1795000</v>
       </c>
       <c r="L14" t="n">
-        <v>9000</v>
+        <v>1883000</v>
       </c>
       <c r="M14" t="n">
-        <v>7690</v>
+        <v>1795000</v>
       </c>
       <c r="N14" t="n">
-        <v>0.41</v>
+        <v>50.63</v>
       </c>
       <c r="O14" t="n">
-        <v>120266040840</v>
+        <v>5976730313500</v>
       </c>
       <c r="P14" t="n">
-        <v>10300</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>952</v>
+        <v>277000</v>
       </c>
       <c r="R14" t="n">
-        <v>-211000</v>
+        <v>180000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>151000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>강력한 지지선 및 신고가 돌파 기대감 존재. 일부는 하락 및 숏커버링 가능성을 언급하며 관망세.</t>
+          <t>개인 매도세 속 기관/외인 매수 유입. 상승 추세 전환 신호 및 악성 매물 소화.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['지지선', '돌파', '숏커버링']</t>
+          <t>['기관 매수', '외인 매수', '상승 추세']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30550</v>
+        <v>91700</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+2.69%</t>
+          <t>+2.46%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.08</v>
+        <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>725</v>
+        <v>363</v>
       </c>
       <c r="F15" t="n">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="G15" t="n">
-        <v>1046</v>
+        <v>1762</v>
       </c>
       <c r="H15" t="n">
-        <v>0.31</v>
+        <v>23.61</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>29750</v>
+        <v>89500</v>
       </c>
       <c r="K15" t="n">
-        <v>31600</v>
+        <v>92000</v>
       </c>
       <c r="L15" t="n">
-        <v>34200</v>
+        <v>94400</v>
       </c>
       <c r="M15" t="n">
-        <v>28300</v>
+        <v>91100</v>
       </c>
       <c r="N15" t="n">
-        <v>0.23</v>
+        <v>23.63</v>
       </c>
       <c r="O15" t="n">
-        <v>529460328575</v>
+        <v>331624140600</v>
       </c>
       <c r="P15" t="n">
-        <v>39350</v>
+        <v>139200</v>
       </c>
       <c r="Q15" t="n">
-        <v>8200</v>
+        <v>57000</v>
       </c>
       <c r="R15" t="n">
-        <v>-1000</v>
+        <v>123000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>96000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>혈압계 관련 뉴스 및 유럽 진출 소식, 주가 반등 기대감.</t>
+          <t>미국 원전주 급등 및 SMR 관련 긍정적 전망. 한-프랑스 정상회담 원자력 협력 기대감 반영. 하반기 주도주 가능성 및 대미 투자 수혜 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['혈압계', '유럽 진출', '최저점']</t>
+          <t>['원전', 'SMR', '한-프랑스']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>91700</v>
+        <v>7820</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+2.46%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.02</v>
+        <v>1.4</v>
       </c>
       <c r="E16" t="n">
-        <v>358</v>
+        <v>145</v>
       </c>
       <c r="F16" t="n">
-        <v>227</v>
+        <v>86</v>
       </c>
       <c r="G16" t="n">
-        <v>1754</v>
+        <v>369</v>
       </c>
       <c r="H16" t="n">
-        <v>23.61</v>
+        <v>1.81</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>89500</v>
+        <v>7680</v>
       </c>
       <c r="K16" t="n">
-        <v>92000</v>
+        <v>7780</v>
       </c>
       <c r="L16" t="n">
-        <v>94400</v>
+        <v>9000</v>
       </c>
       <c r="M16" t="n">
-        <v>91100</v>
+        <v>7690</v>
       </c>
       <c r="N16" t="n">
-        <v>23.63</v>
+        <v>0.41</v>
       </c>
       <c r="O16" t="n">
-        <v>325255660850</v>
+        <v>121183731840</v>
       </c>
       <c r="P16" t="n">
-        <v>139200</v>
+        <v>10300</v>
       </c>
       <c r="Q16" t="n">
-        <v>57000</v>
+        <v>952</v>
       </c>
       <c r="R16" t="n">
-        <v>123000</v>
+        <v>-211000</v>
       </c>
       <c r="S16" t="n">
-        <v>96000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 원전주 급등 및 SMR 관련 긍정적 전망. 한-프랑스 정상회담 원자력 협력 기대감 반영. 하반기 주도주 가능성 및 대미 투자 수혜 언급.</t>
+          <t>강력 지지선 확인 및 상승 중. 레미콘 파업 이슈와 함께 상한가 기대감.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '한-프랑스']</t>
+          <t>['지지선', '레미콘 파업', '상한가 기대']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,90 +1936,90 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12120</v>
+        <v>30200</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>+1.51%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-2.16</v>
+        <v>0.08</v>
       </c>
       <c r="E17" t="n">
-        <v>191</v>
+        <v>749</v>
       </c>
       <c r="F17" t="n">
-        <v>103</v>
+        <v>254</v>
       </c>
       <c r="G17" t="n">
-        <v>435</v>
+        <v>1065</v>
       </c>
       <c r="H17" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>29750</v>
+      </c>
+      <c r="K17" t="n">
+        <v>31600</v>
+      </c>
+      <c r="L17" t="n">
+        <v>34200</v>
+      </c>
+      <c r="M17" t="n">
+        <v>28300</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="O17" t="n">
+        <v>542388000350</v>
+      </c>
+      <c r="P17" t="n">
+        <v>39350</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>8200</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="S17" t="n">
         <v>0</v>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>MarketType.KOSDAQ</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>11990</v>
-      </c>
-      <c r="K17" t="n">
-        <v>12440</v>
-      </c>
-      <c r="L17" t="n">
-        <v>12800</v>
-      </c>
-      <c r="M17" t="n">
-        <v>11920</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="O17" t="n">
-        <v>49177428615</v>
-      </c>
-      <c r="P17" t="n">
-        <v>36200</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>8920</v>
-      </c>
-      <c r="R17" t="n">
-        <v>22000</v>
-      </c>
-      <c r="S17" t="n">
-        <v>-6000</v>
-      </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>국제 유가 급등 및 이란 관련 이슈로 인한 상승 기대감 있으나, 주가는 반응이 없고 오히려 하락했다는 분석 제시.</t>
+          <t>혈압계 관련 뉴스 및 유럽 진출 소식, 주가 반등 기대감.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['국제유가', '이란', '주가 반응']</t>
+          <t>['혈압계', '유럽 진출', '최저점']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,86 +2028,86 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8970</v>
+        <v>12090</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.83%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.36</v>
+        <v>-2.16</v>
       </c>
       <c r="E18" t="n">
-        <v>121</v>
+        <v>192</v>
       </c>
       <c r="F18" t="n">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="G18" t="n">
-        <v>524</v>
+        <v>439</v>
       </c>
       <c r="H18" t="n">
-        <v>27.69</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>8940</v>
+        <v>11990</v>
       </c>
       <c r="K18" t="n">
-        <v>8940</v>
+        <v>12440</v>
       </c>
       <c r="L18" t="n">
-        <v>9070</v>
+        <v>12800</v>
       </c>
       <c r="M18" t="n">
-        <v>8710</v>
+        <v>11920</v>
       </c>
       <c r="N18" t="n">
-        <v>28.05</v>
+        <v>2.16</v>
       </c>
       <c r="O18" t="n">
-        <v>34206964330</v>
+        <v>49930616835</v>
       </c>
       <c r="P18" t="n">
-        <v>17950</v>
+        <v>36200</v>
       </c>
       <c r="Q18" t="n">
-        <v>8120</v>
+        <v>8920</v>
       </c>
       <c r="R18" t="n">
-        <v>-309000</v>
+        <v>22000</v>
       </c>
       <c r="S18" t="n">
-        <v>7000</v>
+        <v>-6000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>기업 실적 및 성장성에 대한 부정적 전망, 투자 비판.</t>
+          <t>국제유가 급등에도 불구하고 흥구석유 주가 움직임은 미미하며, 투자자들은 전쟁 관련 뉴스에 주목하고 있으나 명확한 근거는 부족한 상황이다.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['실적', '성장성', '투자 비판']</t>
+          <t>['국제유가', '흥구석유', '전쟁']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>270000</v>
+        <v>270250</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="F19" t="n">
         <v>489</v>
       </c>
       <c r="G19" t="n">
-        <v>1758</v>
+        <v>1821</v>
       </c>
       <c r="H19" t="n">
         <v>46.85</v>
@@ -2174,7 +2174,7 @@
         <v>46.79</v>
       </c>
       <c r="O19" t="n">
-        <v>3951124796250</v>
+        <v>4018635669250</v>
       </c>
       <c r="P19" t="n">
         <v>374500</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>노조, 이재용 관련 이슈 및 외인 매도세에 대한 부정적 언급과 함께 영업이익 전세계 1위라는 팩트 제시. 주가 하락 및 희망 없는 전망 다수.</t>
+          <t>노조 이슈 및 경영진 관련 부정적 언급 다수. 하이닉스와의 비교 속 주가 부진 우려.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['노조', '외인 매도', '영업이익']</t>
+          <t>['노조', '경영진', '주가 부진']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2219,215 +2219,215 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3870</v>
+        <v>8950</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.52</v>
+        <v>-0.36</v>
       </c>
       <c r="E20" t="n">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="F20" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="G20" t="n">
-        <v>201</v>
+        <v>522</v>
       </c>
       <c r="H20" t="n">
-        <v>2.08</v>
+        <v>27.69</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>3890</v>
+        <v>8940</v>
       </c>
       <c r="K20" t="n">
-        <v>3890</v>
+        <v>8940</v>
       </c>
       <c r="L20" t="n">
-        <v>4115</v>
+        <v>9070</v>
       </c>
       <c r="M20" t="n">
-        <v>3700</v>
+        <v>8710</v>
       </c>
       <c r="N20" t="n">
-        <v>1.56</v>
+        <v>28.05</v>
       </c>
       <c r="O20" t="n">
-        <v>70042091952</v>
+        <v>35220676930</v>
       </c>
       <c r="P20" t="n">
-        <v>4335</v>
+        <v>17950</v>
       </c>
       <c r="Q20" t="n">
-        <v>1246</v>
+        <v>8120</v>
       </c>
       <c r="R20" t="n">
-        <v>-599000</v>
+        <v>-309000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>탈모 관련주로 언급되나 구체적인 재료 및 뉴스 부재, 하락 추세 및 조정 국면.</t>
+          <t>기업 실적 및 성장성에 대한 부정적 전망, 투자 비판.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['탈모주', '하락']</t>
+          <t>['실적', '성장성', '투자 비판']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>33750</v>
+        <v>3865</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.1</v>
+        <v>0.52</v>
       </c>
       <c r="E21" t="n">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="F21" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="G21" t="n">
-        <v>324</v>
+        <v>209</v>
       </c>
       <c r="H21" t="n">
-        <v>52.55</v>
+        <v>2.08</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>34100</v>
+        <v>3890</v>
       </c>
       <c r="K21" t="n">
-        <v>34450</v>
+        <v>3890</v>
       </c>
       <c r="L21" t="n">
-        <v>35325</v>
+        <v>4115</v>
       </c>
       <c r="M21" t="n">
-        <v>33550</v>
+        <v>3700</v>
       </c>
       <c r="N21" t="n">
-        <v>21.01</v>
+        <v>1.56</v>
       </c>
       <c r="O21" t="n">
-        <v>86575259200</v>
+        <v>71702919453</v>
       </c>
       <c r="P21" t="n">
-        <v>69500</v>
+        <v>4335</v>
       </c>
       <c r="Q21" t="n">
-        <v>30400</v>
+        <v>1246</v>
       </c>
       <c r="R21" t="n">
-        <v>-80000</v>
+        <v>-599000</v>
       </c>
       <c r="S21" t="n">
-        <v>58000</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 원전 협력 및 발전 5사 통합, 25조 선납매 관련 긍정적 이슈 언급. 공매도 세력 및 20년째 주주 피해 상황으로 부정적 전망도 제시.</t>
+          <t>탈모 관련주로 언급되나 구체적인 재료 및 뉴스 부재, 하락 추세 및 조정 국면.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전', '발전 5사 통합', '공매도']</t>
+          <t>['탈모주', '하락']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10200</v>
+        <v>33750</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.30%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.32</v>
+        <v>0.1</v>
       </c>
       <c r="E22" t="n">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="F22" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G22" t="n">
-        <v>257</v>
+        <v>330</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9399999999999999</v>
+        <v>52.56</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,91 +2435,91 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>10440</v>
+        <v>34100</v>
       </c>
       <c r="K22" t="n">
-        <v>10180</v>
+        <v>34450</v>
       </c>
       <c r="L22" t="n">
-        <v>11340</v>
+        <v>35325</v>
       </c>
       <c r="M22" t="n">
-        <v>9980</v>
+        <v>33550</v>
       </c>
       <c r="N22" t="n">
-        <v>0.62</v>
+        <v>21.01</v>
       </c>
       <c r="O22" t="n">
-        <v>149740010280</v>
+        <v>87628386400</v>
       </c>
       <c r="P22" t="n">
-        <v>15960</v>
+        <v>69500</v>
       </c>
       <c r="Q22" t="n">
-        <v>3500</v>
+        <v>30400</v>
       </c>
       <c r="R22" t="n">
-        <v>-50000</v>
+        <v>-80000</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>58000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>미증시 제약바이오와는 다른 움직임, 탈모주 관련 기대감 있으나 구체적인 재료 및 공시 부재.</t>
+          <t>미국 원전 협력 및 한전 발전 5사 통합 긍정적 뉴스. 25조 선납매 및 SMP 급락 우려.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['탈모주', '재료']</t>
+          <t>['원전 협력', '발전 5사 통합', 'SMP']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>015760</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19450</v>
+        <v>10270</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.60%</t>
+          <t>-1.63%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="E23" t="n">
-        <v>254</v>
+        <v>109</v>
       </c>
       <c r="F23" t="n">
-        <v>130</v>
+        <v>71</v>
       </c>
       <c r="G23" t="n">
-        <v>777</v>
+        <v>260</v>
       </c>
       <c r="H23" t="n">
-        <v>10.85</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,58 +2527,150 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>19970</v>
+        <v>10440</v>
       </c>
       <c r="K23" t="n">
-        <v>20250</v>
+        <v>10180</v>
       </c>
       <c r="L23" t="n">
-        <v>21300</v>
+        <v>11340</v>
       </c>
       <c r="M23" t="n">
-        <v>19350</v>
+        <v>9980</v>
       </c>
       <c r="N23" t="n">
-        <v>10.47</v>
+        <v>0.62</v>
       </c>
       <c r="O23" t="n">
-        <v>289449585835</v>
+        <v>152241849525</v>
       </c>
       <c r="P23" t="n">
-        <v>40350</v>
+        <v>15960</v>
       </c>
       <c r="Q23" t="n">
-        <v>3320</v>
+        <v>3500</v>
       </c>
       <c r="R23" t="n">
-        <v>-1107000</v>
+        <v>-50000</v>
       </c>
       <c r="S23" t="n">
-        <v>-209000</v>
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>원전 관련 호재 속 계약 체결 공시 확인, 일부 투자자 기대감.</t>
+          <t>미증시 제약바이오와는 다른 움직임, 탈모주 관련 기대감 있으나 구체적인 재료 및 공시 부재.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>['탈모주', '재료']</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>004310</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>19440</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>-2.65%</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E24" t="n">
+        <v>261</v>
+      </c>
+      <c r="F24" t="n">
+        <v>131</v>
+      </c>
+      <c r="G24" t="n">
+        <v>792</v>
+      </c>
+      <c r="H24" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>19970</v>
+      </c>
+      <c r="K24" t="n">
+        <v>20250</v>
+      </c>
+      <c r="L24" t="n">
+        <v>21300</v>
+      </c>
+      <c r="M24" t="n">
+        <v>19350</v>
+      </c>
+      <c r="N24" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="O24" t="n">
+        <v>294861460090</v>
+      </c>
+      <c r="P24" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-1107000</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-209000</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>원전 관련 호재 속 계약 체결 공시 확인, 일부 투자자 기대감.</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="n">
         <v>0.3</v>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>['원전', '공시', '계약체결']</t>
         </is>
       </c>
-      <c r="X23" t="n">
+      <c r="X24" t="n">
         <v>12</v>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>047040</t>
         </is>

--- a/data/trending_integrated_20260909_15.xlsx
+++ b/data/trending_integrated_20260909_15.xlsx
@@ -578,13 +578,13 @@
         <v>-1.06</v>
       </c>
       <c r="E2" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F2" t="n">
         <v>135</v>
       </c>
       <c r="G2" t="n">
-        <v>1683</v>
+        <v>1713</v>
       </c>
       <c r="H2" t="n">
         <v>0.77</v>
@@ -610,7 +610,7 @@
         <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>29784514335</v>
+        <v>29788795675</v>
       </c>
       <c r="P2" t="n">
         <v>21500</v>
@@ -670,13 +670,13 @@
         <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F3" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G3" t="n">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="H3" t="n">
         <v>0.36</v>
@@ -702,7 +702,7 @@
         <v>0.44</v>
       </c>
       <c r="O3" t="n">
-        <v>233465315215</v>
+        <v>233498007485</v>
       </c>
       <c r="P3" t="n">
         <v>20850</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 증시 SMR 관련주 폭등에 따른 기대감, 품절주 특성 언급.</t>
+          <t>SMR 관련주 폭등 및 삼미금속 목표가 상승 전망. 정부 대미 투자 및 가스터빈 관련 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['SMR', '품절주', '가스터빈']</t>
+          <t>['SMR', '삼미금속', '가스터빈']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,13 +762,13 @@
         <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F4" t="n">
         <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="H4" t="n">
         <v>2.46</v>
@@ -794,7 +794,7 @@
         <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>37978952115</v>
+        <v>37984628595</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14290</v>
+        <v>14320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+21.00%</t>
+          <t>+21.25%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.22</v>
       </c>
       <c r="E5" t="n">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F5" t="n">
         <v>176</v>
       </c>
       <c r="G5" t="n">
-        <v>1575</v>
+        <v>1620</v>
       </c>
       <c r="H5" t="n">
         <v>5.64</v>
@@ -886,7 +886,7 @@
         <v>5.42</v>
       </c>
       <c r="O5" t="n">
-        <v>522857428495</v>
+        <v>530428985295</v>
       </c>
       <c r="P5" t="n">
         <v>30200</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 원전주 강세 및 체코, 사우디 관련 이슈 언급. 하반기 주도주, 단기 급등 전망 제시하며 긍정적 논조 강화.</t>
+          <t>원전 및 로봇 관련주 상승 전망. 단기 목표가 제시 및 외국 자본 유입 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전', '체코', '사우디']</t>
+          <t>['원전', '로봇', '목표가']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7150</v>
+        <v>7130</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+14.22%</t>
+          <t>+13.90%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="F6" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G6" t="n">
-        <v>1339</v>
+        <v>1360</v>
       </c>
       <c r="H6" t="n">
         <v>7.4</v>
@@ -978,7 +978,7 @@
         <v>7.35</v>
       </c>
       <c r="O6" t="n">
-        <v>71771967855</v>
+        <v>72172966185</v>
       </c>
       <c r="P6" t="n">
         <v>21500</v>
@@ -1038,13 +1038,13 @@
         <v>0.03</v>
       </c>
       <c r="E7" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F7" t="n">
         <v>128</v>
       </c>
       <c r="G7" t="n">
-        <v>660</v>
+        <v>676</v>
       </c>
       <c r="H7" t="n">
         <v>14.96</v>
@@ -1070,7 +1070,7 @@
         <v>14.93</v>
       </c>
       <c r="O7" t="n">
-        <v>167660719050</v>
+        <v>168662127150</v>
       </c>
       <c r="P7" t="n">
         <v>108900</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>대규모 수주 및 2분기 영업이익 흑자 전환 기대감. 목표가 상향 논의 활발.</t>
+          <t>두산퓨얼셀, 2분기 실적 부진에도 불구하고 목표가 상향 및 수주 기대감으로 인한 단기 상승세.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['수주', '영업이익', '목표가']</t>
+          <t>['수주', '목표가', '실적']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1130,13 +1130,13 @@
         <v>-0.39</v>
       </c>
       <c r="E8" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F8" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G8" t="n">
-        <v>1565</v>
+        <v>1604</v>
       </c>
       <c r="H8" t="n">
         <v>1.55</v>
@@ -1162,7 +1162,7 @@
         <v>1.94</v>
       </c>
       <c r="O8" t="n">
-        <v>447240616025</v>
+        <v>449834620185</v>
       </c>
       <c r="P8" t="n">
         <v>31500</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2090</v>
+        <v>2085</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+8.74%</t>
+          <t>+8.48%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.1</v>
       </c>
       <c r="E9" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F9" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G9" t="n">
-        <v>324</v>
+        <v>350</v>
       </c>
       <c r="H9" t="n">
         <v>0.51</v>
@@ -1254,7 +1254,7 @@
         <v>0.61</v>
       </c>
       <c r="O9" t="n">
-        <v>18309827760</v>
+        <v>18426089445</v>
       </c>
       <c r="P9" t="n">
         <v>2930</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>반도체 클러스터 대장주 언급 및 텐버거 찌라시. 대주주 매도 공시 및 물량 넘기기 우려.</t>
+          <t>강동씨앤엘, 반도체 클러스터 대장주 부각 속 대주주 매도 공시로 인한 단기 변동성 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['반도체 클러스터', '텐버거', '대주주 매도']</t>
+          <t>['반도체', '대주주매도', '전망']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6850</v>
+        <v>6860</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+6.53%</t>
+          <t>+6.69%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>136</v>
       </c>
       <c r="G10" t="n">
-        <v>528</v>
+        <v>509</v>
       </c>
       <c r="H10" t="n">
         <v>16.71</v>
@@ -1346,7 +1346,7 @@
         <v>16.4</v>
       </c>
       <c r="O10" t="n">
-        <v>102089843410</v>
+        <v>102686244950</v>
       </c>
       <c r="P10" t="n">
         <v>13000</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>배당금 대비 낮은 주가 및 시총 관련 논의. 거래량 증가와 함께 일부 상승 기대감.</t>
+          <t>배당 및 주가 부진에 대한 언급. 투자자들의 실망감 표출.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['배당금', '시가총액', '거래량']</t>
+          <t>['배당', '주가', '실망감']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8340</v>
+        <v>8350</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+5.97%</t>
+          <t>+6.10%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.46</v>
       </c>
       <c r="E11" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F11" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H11" t="n">
         <v>39.3</v>
@@ -1438,7 +1438,7 @@
         <v>38.84</v>
       </c>
       <c r="O11" t="n">
-        <v>42363747010</v>
+        <v>42724951310</v>
       </c>
       <c r="P11" t="n">
         <v>19150</v>
@@ -1483,83 +1483,83 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2260</v>
+        <v>3810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+4.63%</t>
+          <t>+4.67%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.23</v>
+        <v>2.74</v>
       </c>
       <c r="E12" t="n">
-        <v>200</v>
+        <v>248</v>
       </c>
       <c r="F12" t="n">
-        <v>86</v>
+        <v>133</v>
       </c>
       <c r="G12" t="n">
-        <v>397</v>
+        <v>573</v>
       </c>
       <c r="H12" t="n">
-        <v>5.26</v>
+        <v>3.19</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>2160</v>
+        <v>3640</v>
       </c>
       <c r="K12" t="n">
-        <v>2200</v>
+        <v>3750</v>
       </c>
       <c r="L12" t="n">
-        <v>2705</v>
+        <v>4460</v>
       </c>
       <c r="M12" t="n">
-        <v>2130</v>
+        <v>3680</v>
       </c>
       <c r="N12" t="n">
-        <v>5.49</v>
+        <v>0.45</v>
       </c>
       <c r="O12" t="n">
-        <v>47851656010</v>
+        <v>278852496482</v>
       </c>
       <c r="P12" t="n">
-        <v>2705</v>
+        <v>8100</v>
       </c>
       <c r="Q12" t="n">
-        <v>1418</v>
+        <v>592</v>
       </c>
       <c r="R12" t="n">
-        <v>22000</v>
+        <v>-731000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>지분 싸움 및 기타법인 장내매수 포착. 단기 과열 우려 속 변동성 확대.</t>
+          <t>광통신 관련주 급등 및 빛과전자 강세 전망. 6G 기반 기술 및 글로벌 공급 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['지분 싸움', '장내매수', '단기 과열']</t>
+          <t>['광통신', '빛과전자', '6G']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3805</v>
+        <v>2260</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+4.53%</t>
+          <t>+4.63%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2.74</v>
+        <v>-0.23</v>
       </c>
       <c r="E13" t="n">
-        <v>245</v>
+        <v>205</v>
       </c>
       <c r="F13" t="n">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="G13" t="n">
-        <v>562</v>
+        <v>422</v>
       </c>
       <c r="H13" t="n">
-        <v>3.19</v>
+        <v>5.26</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>3640</v>
+        <v>2160</v>
       </c>
       <c r="K13" t="n">
-        <v>3750</v>
+        <v>2200</v>
       </c>
       <c r="L13" t="n">
-        <v>4460</v>
+        <v>2705</v>
       </c>
       <c r="M13" t="n">
-        <v>3680</v>
+        <v>2130</v>
       </c>
       <c r="N13" t="n">
-        <v>0.45</v>
+        <v>5.49</v>
       </c>
       <c r="O13" t="n">
-        <v>277930731752</v>
+        <v>48057169110</v>
       </c>
       <c r="P13" t="n">
-        <v>8100</v>
+        <v>2705</v>
       </c>
       <c r="Q13" t="n">
-        <v>592</v>
+        <v>1418</v>
       </c>
       <c r="R13" t="n">
-        <v>-731000</v>
+        <v>22000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 광통신 섹터 급등에 따른 기대감. 글로벌 회사 대량 공급 뉴스 및 6G 기반 재료.</t>
+          <t>지분 싸움과 기타 법인 장내 매수 관련 언급. 일부 투자자는 하락 예측.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['광통신', '글로벌 공급', '6G']</t>
+          <t>['지분 싸움', '장내매수', '투자']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1858000</v>
+        <v>1856000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+3.63%</t>
+          <t>+3.51%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="F14" t="n">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G14" t="n">
-        <v>2124</v>
+        <v>2145</v>
       </c>
       <c r="H14" t="n">
         <v>50.66</v>
@@ -1714,7 +1714,7 @@
         <v>50.63</v>
       </c>
       <c r="O14" t="n">
-        <v>5976730313500</v>
+        <v>6512518537500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>개인 매도세 속 기관/외인 매수 유입. 상승 추세 전환 신호 및 악성 매물 소화.</t>
+          <t>SK하이닉스 상승 추세 전환 신호 및 목표가 상승 전망. 수급 및 악성매물 소화 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['기관 매수', '외인 매수', '상승 추세']</t>
+          <t>['SK하이닉스', '상승 추세', '수급']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1774,13 +1774,13 @@
         <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F15" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G15" t="n">
-        <v>1762</v>
+        <v>1775</v>
       </c>
       <c r="H15" t="n">
         <v>23.61</v>
@@ -1806,7 +1806,7 @@
         <v>23.63</v>
       </c>
       <c r="O15" t="n">
-        <v>331624140600</v>
+        <v>343506810000</v>
       </c>
       <c r="P15" t="n">
         <v>139200</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7820</v>
+        <v>7830</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+1.82%</t>
+          <t>+1.95%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1.4</v>
       </c>
       <c r="E16" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F16" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G16" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="H16" t="n">
         <v>1.81</v>
@@ -1898,7 +1898,7 @@
         <v>0.41</v>
       </c>
       <c r="O16" t="n">
-        <v>121183731840</v>
+        <v>121380006450</v>
       </c>
       <c r="P16" t="n">
         <v>10300</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30200</v>
+        <v>30300</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+1.51%</t>
+          <t>+1.85%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.08</v>
       </c>
       <c r="E17" t="n">
-        <v>749</v>
+        <v>762</v>
       </c>
       <c r="F17" t="n">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="G17" t="n">
-        <v>1065</v>
+        <v>1091</v>
       </c>
       <c r="H17" t="n">
         <v>0.31</v>
@@ -1990,7 +1990,7 @@
         <v>0.23</v>
       </c>
       <c r="O17" t="n">
-        <v>542388000350</v>
+        <v>544717252250</v>
       </c>
       <c r="P17" t="n">
         <v>39350</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>혈압계 관련 뉴스 및 유럽 진출 소식, 주가 반등 기대감.</t>
+          <t>혈압 반기 관련 기술 및 유럽 진출 뉴스. 주가 최저점 및 반등 기대.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['혈압계', '유럽 진출', '최저점']</t>
+          <t>['혈압 반지', '스카이랩스', '유럽 진출']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2050,13 +2050,13 @@
         <v>-2.16</v>
       </c>
       <c r="E18" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F18" t="n">
         <v>104</v>
       </c>
       <c r="G18" t="n">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2082,7 +2082,7 @@
         <v>2.16</v>
       </c>
       <c r="O18" t="n">
-        <v>49930616835</v>
+        <v>50268749955</v>
       </c>
       <c r="P18" t="n">
         <v>36200</v>
@@ -2127,31 +2127,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>270250</v>
+        <v>8950</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.06</v>
+        <v>-0.36</v>
       </c>
       <c r="E19" t="n">
-        <v>785</v>
+        <v>123</v>
       </c>
       <c r="F19" t="n">
-        <v>489</v>
+        <v>67</v>
       </c>
       <c r="G19" t="n">
-        <v>1821</v>
+        <v>523</v>
       </c>
       <c r="H19" t="n">
-        <v>46.85</v>
+        <v>27.69</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>269500</v>
+        <v>8940</v>
       </c>
       <c r="K19" t="n">
-        <v>269500</v>
+        <v>8940</v>
       </c>
       <c r="L19" t="n">
-        <v>275000</v>
+        <v>9070</v>
       </c>
       <c r="M19" t="n">
-        <v>267500</v>
+        <v>8710</v>
       </c>
       <c r="N19" t="n">
-        <v>46.79</v>
+        <v>28.05</v>
       </c>
       <c r="O19" t="n">
-        <v>4018635669250</v>
+        <v>37459877430</v>
       </c>
       <c r="P19" t="n">
-        <v>374500</v>
+        <v>17950</v>
       </c>
       <c r="Q19" t="n">
-        <v>70000</v>
+        <v>8120</v>
       </c>
       <c r="R19" t="n">
-        <v>-1876000</v>
+        <v>-309000</v>
       </c>
       <c r="S19" t="n">
-        <v>784000</v>
+        <v>7000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>노조 이슈 및 경영진 관련 부정적 언급 다수. 하이닉스와의 비교 속 주가 부진 우려.</t>
+          <t>LG디스플레이 주가 부진 및 매도 의견. AI 및 중국산 영향 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['노조', '경영진', '주가 부진']</t>
+          <t>['LG디스플레이', '주가', '매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8950</v>
+        <v>269500</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.36</v>
+        <v>0.06</v>
       </c>
       <c r="E20" t="n">
-        <v>121</v>
+        <v>785</v>
       </c>
       <c r="F20" t="n">
-        <v>68</v>
+        <v>475</v>
       </c>
       <c r="G20" t="n">
-        <v>522</v>
+        <v>1997</v>
       </c>
       <c r="H20" t="n">
-        <v>27.69</v>
+        <v>46.85</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,38 +2251,38 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>8940</v>
+        <v>269500</v>
       </c>
       <c r="K20" t="n">
-        <v>8940</v>
+        <v>269500</v>
       </c>
       <c r="L20" t="n">
-        <v>9070</v>
+        <v>275000</v>
       </c>
       <c r="M20" t="n">
-        <v>8710</v>
+        <v>267500</v>
       </c>
       <c r="N20" t="n">
-        <v>28.05</v>
+        <v>46.79</v>
       </c>
       <c r="O20" t="n">
-        <v>35220676930</v>
+        <v>4357725689750</v>
       </c>
       <c r="P20" t="n">
-        <v>17950</v>
+        <v>374500</v>
       </c>
       <c r="Q20" t="n">
-        <v>8120</v>
+        <v>70000</v>
       </c>
       <c r="R20" t="n">
-        <v>-309000</v>
+        <v>-1876000</v>
       </c>
       <c r="S20" t="n">
-        <v>7000</v>
+        <v>784000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>기업 실적 및 성장성에 대한 부정적 전망, 투자 비판.</t>
+          <t>삼성전자 주가 부진에 대한 부정적 의견 및 하이닉스와의 비교. 노조 및 경영진 관련 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['실적', '성장성', '투자 비판']</t>
+          <t>['삼성전자', '하이닉스', '주가']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -2326,13 +2326,13 @@
         <v>0.52</v>
       </c>
       <c r="E21" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F21" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G21" t="n">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="H21" t="n">
         <v>2.08</v>
@@ -2358,7 +2358,7 @@
         <v>1.56</v>
       </c>
       <c r="O21" t="n">
-        <v>71702919453</v>
+        <v>72177549183</v>
       </c>
       <c r="P21" t="n">
         <v>4335</v>
@@ -2418,7 +2418,7 @@
         <v>0.1</v>
       </c>
       <c r="E22" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F22" t="n">
         <v>67</v>
@@ -2427,7 +2427,7 @@
         <v>330</v>
       </c>
       <c r="H22" t="n">
-        <v>52.56</v>
+        <v>52.55</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>21.01</v>
       </c>
       <c r="O22" t="n">
-        <v>87628386400</v>
+        <v>89776303900</v>
       </c>
       <c r="P22" t="n">
         <v>69500</v>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10270</v>
+        <v>10300</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>-1.34%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.32</v>
       </c>
       <c r="E23" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F23" t="n">
         <v>71</v>
       </c>
       <c r="G23" t="n">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H23" t="n">
         <v>0.9399999999999999</v>
@@ -2542,7 +2542,7 @@
         <v>0.62</v>
       </c>
       <c r="O23" t="n">
-        <v>152241849525</v>
+        <v>153244503025</v>
       </c>
       <c r="P23" t="n">
         <v>15960</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>19440</v>
+        <v>19450</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-2.65%</t>
+          <t>-2.60%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0.38</v>
       </c>
       <c r="E24" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F24" t="n">
         <v>131</v>
       </c>
       <c r="G24" t="n">
-        <v>792</v>
+        <v>779</v>
       </c>
       <c r="H24" t="n">
         <v>10.85</v>
@@ -2634,7 +2634,7 @@
         <v>10.47</v>
       </c>
       <c r="O24" t="n">
-        <v>294861460090</v>
+        <v>296687153790</v>
       </c>
       <c r="P24" t="n">
         <v>40350</v>
@@ -2650,16 +2650,16 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>원전 관련 호재 속 계약 체결 공시 확인, 일부 투자자 기대감.</t>
+          <t>원전 관련주 상승 및 대우건설 적정가 논의. 계약 체결 공시 언급.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['원전', '공시', '계약체결']</t>
+          <t>['원전', '계약', '적정가']</t>
         </is>
       </c>
       <c r="X24" t="n">

--- a/data/trending_integrated_20260909_15.xlsx
+++ b/data/trending_integrated_20260909_15.xlsx
@@ -578,13 +578,13 @@
         <v>-1.06</v>
       </c>
       <c r="E2" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F2" t="n">
         <v>135</v>
       </c>
       <c r="G2" t="n">
-        <v>1713</v>
+        <v>1746</v>
       </c>
       <c r="H2" t="n">
         <v>0.77</v>
@@ -610,7 +610,7 @@
         <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>29788795675</v>
+        <v>29788869875</v>
       </c>
       <c r="P2" t="n">
         <v>21500</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미 FDA 2A상 승인 기대감 및 병용요법 연구 결과 공개 예정. 외국인 매수세 유입.</t>
+          <t>페니트리움바이오, 미국 FDA 2A상 승인 및 뎅기열 치료제 글로벌 임상 결과 발표 기대감 고조. 다락손라십 대비 우수한 효능 및 병용 확장 전략에 대한 긍정적 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['FDA 2A상', '병용요법', '외국인 매수']</t>
+          <t>['FDA', '뎅기열', '병용 확장']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F3" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G3" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H3" t="n">
         <v>0.36</v>
@@ -702,7 +702,7 @@
         <v>0.44</v>
       </c>
       <c r="O3" t="n">
-        <v>233498007485</v>
+        <v>233499141095</v>
       </c>
       <c r="P3" t="n">
         <v>20850</v>
@@ -768,7 +768,7 @@
         <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="H4" t="n">
         <v>2.46</v>
@@ -854,13 +854,13 @@
         <v>0.22</v>
       </c>
       <c r="E5" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F5" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G5" t="n">
-        <v>1620</v>
+        <v>1652</v>
       </c>
       <c r="H5" t="n">
         <v>5.64</v>
@@ -886,7 +886,7 @@
         <v>5.42</v>
       </c>
       <c r="O5" t="n">
-        <v>530428985295</v>
+        <v>530851410975</v>
       </c>
       <c r="P5" t="n">
         <v>30200</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>원전 및 로봇 관련주 상승 전망. 단기 목표가 제시 및 외국 자본 유입 언급.</t>
+          <t>우리기술, 체코 원전 수주 기대감 및 하반기 주도주 전망. 정부 정책 및 외국 자본 유입 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전', '로봇', '목표가']</t>
+          <t>['원전', '수주', '정책']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -946,13 +946,13 @@
         <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F6" t="n">
         <v>123</v>
       </c>
       <c r="G6" t="n">
-        <v>1360</v>
+        <v>1399</v>
       </c>
       <c r="H6" t="n">
         <v>7.4</v>
@@ -978,7 +978,7 @@
         <v>7.35</v>
       </c>
       <c r="O6" t="n">
-        <v>72172966185</v>
+        <v>72186149555</v>
       </c>
       <c r="P6" t="n">
         <v>21500</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>뎅기열, 췌장암 치료제 등 신약 개발 기대감 및 공매도와의 경쟁.</t>
+          <t>현대바이오, 공매도 세력과의 경쟁 속 뎅기열 및 췌장암 치료제 관련 실험 결과 발표 기대감 고조. 페니트리움바이오의 최대 주주로서 전립선 치료제 데이터 발표에 대한 전망도 긍정적.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['신약 개발', '공매도', '임상 결과']</t>
+          <t>['뎅기열', '췌장암', '전립선']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1044,7 +1044,7 @@
         <v>128</v>
       </c>
       <c r="G7" t="n">
-        <v>676</v>
+        <v>698</v>
       </c>
       <c r="H7" t="n">
         <v>14.96</v>
@@ -1070,7 +1070,7 @@
         <v>14.93</v>
       </c>
       <c r="O7" t="n">
-        <v>168662127150</v>
+        <v>168678782250</v>
       </c>
       <c r="P7" t="n">
         <v>108900</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>두산퓨얼셀, 2분기 실적 부진에도 불구하고 목표가 상향 및 수주 기대감으로 인한 단기 상승세.</t>
+          <t>두산퓨얼셀, 수주 건 확인 및 2분기 영업이익 부진에도 불구하고 향후 매출 성장성 및 목표가 상향 조정에 대한 기대감 형성. 기관 및 외인 매수세 유입 가능성 논의.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['수주', '목표가', '실적']</t>
+          <t>['수주', '영업이익', '매출 성장성']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1136,7 +1136,7 @@
         <v>170</v>
       </c>
       <c r="G8" t="n">
-        <v>1604</v>
+        <v>1635</v>
       </c>
       <c r="H8" t="n">
         <v>1.55</v>
@@ -1162,7 +1162,7 @@
         <v>1.94</v>
       </c>
       <c r="O8" t="n">
-        <v>449834620185</v>
+        <v>450052497625</v>
       </c>
       <c r="P8" t="n">
         <v>31500</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>빛과전자 수급 흡수 및 개인 매도세 속 상승 기대. 단기 박스권 돌파 및 우상향 추세.</t>
+          <t>대한광통신, 빛과전자와의 수급 연계 및 차트상 우상향 추세 분석. 외인, 기관, 투신 매수세 유입 및 박스권 돌파.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['수급', '단기 박스권', '우상향']</t>
+          <t>['수급', '차트', '매수세']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1222,13 +1222,13 @@
         <v>-0.1</v>
       </c>
       <c r="E9" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F9" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G9" t="n">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="H9" t="n">
         <v>0.51</v>
@@ -1254,7 +1254,7 @@
         <v>0.61</v>
       </c>
       <c r="O9" t="n">
-        <v>18426089445</v>
+        <v>18440617725</v>
       </c>
       <c r="P9" t="n">
         <v>2930</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>강동씨앤엘, 반도체 클러스터 대장주 부각 속 대주주 매도 공시로 인한 단기 변동성 우려.</t>
+          <t>강동씨앤엘, 시멘트 공급 경쟁력 언급 및 반도체 사업 전환 가능성에 대한 기대감 형성. 대주주 매도 공시 이후 주가 변동성 및 향후 전망에 대한 논의.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['반도체', '대주주매도', '전망']</t>
+          <t>['시멘트', '반도체', '대주주 매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1314,13 +1314,13 @@
         <v>0.31</v>
       </c>
       <c r="E10" t="n">
-        <v>299</v>
+        <v>158</v>
       </c>
       <c r="F10" t="n">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="G10" t="n">
-        <v>509</v>
+        <v>315</v>
       </c>
       <c r="H10" t="n">
         <v>16.71</v>
@@ -1346,7 +1346,7 @@
         <v>16.4</v>
       </c>
       <c r="O10" t="n">
-        <v>102686244950</v>
+        <v>102689366250</v>
       </c>
       <c r="P10" t="n">
         <v>13000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>배당 및 주가 부진에 대한 언급. 투자자들의 실망감 표출.</t>
+          <t>한화머시너리앤서비스홀딩스, 배당 관련 논의 및 주가 하락에 대한 실망감 표현. 거래량 증가 및 손바뀜 가능성 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['배당', '주가', '실망감']</t>
+          <t>['배당', '거래량', '주가']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1412,7 +1412,7 @@
         <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="H11" t="n">
         <v>39.3</v>
@@ -1438,7 +1438,7 @@
         <v>38.84</v>
       </c>
       <c r="O11" t="n">
-        <v>42724951310</v>
+        <v>42739037760</v>
       </c>
       <c r="P11" t="n">
         <v>19150</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>물량 터는 중이라는 의견과 함께 급락. 상패 직전 우려 및 유증 재료 소멸.</t>
+          <t>피노, 급격한 하락세 속 상폐 가능성 및 거래량 증가에 대한 우려 제기. 유상증자 재료 소멸 후 하방 압력 지속 및 투자자들의 부정적 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['물량 터는 중', '급락', '유증 재료 소멸']</t>
+          <t>['상폐', '거래량', '유상증자']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1501,10 +1501,10 @@
         <v>248</v>
       </c>
       <c r="F12" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G12" t="n">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="H12" t="n">
         <v>3.19</v>
@@ -1530,7 +1530,7 @@
         <v>0.45</v>
       </c>
       <c r="O12" t="n">
-        <v>278852496482</v>
+        <v>278916980732</v>
       </c>
       <c r="P12" t="n">
         <v>8100</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>광통신 관련주 급등 및 빛과전자 강세 전망. 6G 기반 기술 및 글로벌 공급 언급.</t>
+          <t>빛과전자, 미국 광통신주 급등에 따른 기대감. 글로벌 회사 대량 공급 뉴스 및 6G 기반 기술 관련 긍정적 전망. 투기과열종목 지정 우려.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', '빛과전자', '6G']</t>
+          <t>['광통신', '6G', '뉴스']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1590,13 +1590,13 @@
         <v>-0.23</v>
       </c>
       <c r="E13" t="n">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="F13" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G13" t="n">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="H13" t="n">
         <v>5.26</v>
@@ -1622,7 +1622,7 @@
         <v>5.49</v>
       </c>
       <c r="O13" t="n">
-        <v>48057169110</v>
+        <v>48077305710</v>
       </c>
       <c r="P13" t="n">
         <v>2705</v>
@@ -1682,13 +1682,13 @@
         <v>0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F14" t="n">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="G14" t="n">
-        <v>2145</v>
+        <v>2165</v>
       </c>
       <c r="H14" t="n">
         <v>50.66</v>
@@ -1714,7 +1714,7 @@
         <v>50.63</v>
       </c>
       <c r="O14" t="n">
-        <v>6512518537500</v>
+        <v>6513090185500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>SK하이닉스 상승 추세 전환 신호 및 목표가 상승 전망. 수급 및 악성매물 소화 언급.</t>
+          <t>SK하이닉스, 상승 추세 전환 신호 포착 및 60일선 돌파 기대감. 기관 및 외국인 매수세 유입 확인. 악성 매물 소화.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '상승 추세', '수급']</t>
+          <t>['상승추세', '기관', '외국인']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1774,13 +1774,13 @@
         <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="F15" t="n">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="G15" t="n">
-        <v>1775</v>
+        <v>1811</v>
       </c>
       <c r="H15" t="n">
         <v>23.61</v>
@@ -1806,7 +1806,7 @@
         <v>23.63</v>
       </c>
       <c r="O15" t="n">
-        <v>343506810000</v>
+        <v>343511670100</v>
       </c>
       <c r="P15" t="n">
         <v>139200</v>
@@ -1866,13 +1866,13 @@
         <v>1.4</v>
       </c>
       <c r="E16" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F16" t="n">
         <v>89</v>
       </c>
       <c r="G16" t="n">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="H16" t="n">
         <v>1.81</v>
@@ -1898,7 +1898,7 @@
         <v>0.41</v>
       </c>
       <c r="O16" t="n">
-        <v>121380006450</v>
+        <v>121407795120</v>
       </c>
       <c r="P16" t="n">
         <v>10300</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>강력 지지선 확인 및 상승 중. 레미콘 파업 이슈와 함께 상한가 기대감.</t>
+          <t>서산, 레미콘 파업 시작에 따른 기대감. 8200선 지지 및 주가 상승 흐름 분석. 개미 꼬시기 및 물갈이 정황.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['지지선', '레미콘 파업', '상한가 기대']</t>
+          <t>['레미콘', '파업', '주가']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1958,13 +1958,13 @@
         <v>0.08</v>
       </c>
       <c r="E17" t="n">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="F17" t="n">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="G17" t="n">
-        <v>1091</v>
+        <v>1106</v>
       </c>
       <c r="H17" t="n">
         <v>0.31</v>
@@ -1990,7 +1990,7 @@
         <v>0.23</v>
       </c>
       <c r="O17" t="n">
-        <v>544717252250</v>
+        <v>545161722950</v>
       </c>
       <c r="P17" t="n">
         <v>39350</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>혈압 반기 관련 기술 및 유럽 진출 뉴스. 주가 최저점 및 반등 기대.</t>
+          <t>스카이랩스, 혈압 반지의 유럽 진출 뉴스 언급. 주가 급락 및 상장폐지 가능성에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['혈압 반지', '스카이랩스', '유럽 진출']</t>
+          <t>['혈압반지', '유럽진출', '주가']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2050,13 +2050,13 @@
         <v>-2.16</v>
       </c>
       <c r="E18" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F18" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G18" t="n">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2082,7 +2082,7 @@
         <v>2.16</v>
       </c>
       <c r="O18" t="n">
-        <v>50268749955</v>
+        <v>50281601625</v>
       </c>
       <c r="P18" t="n">
         <v>36200</v>
@@ -2142,10 +2142,10 @@
         <v>-0.36</v>
       </c>
       <c r="E19" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F19" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G19" t="n">
         <v>523</v>
@@ -2174,7 +2174,7 @@
         <v>28.05</v>
       </c>
       <c r="O19" t="n">
-        <v>37459877430</v>
+        <v>37473293480</v>
       </c>
       <c r="P19" t="n">
         <v>17950</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>LG디스플레이 주가 부진 및 매도 의견. AI 및 중국산 영향 언급.</t>
+          <t>LG디스플레이, 주가 부진 및 중국산 경쟁력 약화에 대한 부정적 전망. AI 및 차세대 기술 관련 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['LG디스플레이', '주가', '매도']</t>
+          <t>['주가', '중국산', 'AI']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2234,13 +2234,13 @@
         <v>0.06</v>
       </c>
       <c r="E20" t="n">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="F20" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G20" t="n">
-        <v>1997</v>
+        <v>2015</v>
       </c>
       <c r="H20" t="n">
         <v>46.85</v>
@@ -2266,7 +2266,7 @@
         <v>46.79</v>
       </c>
       <c r="O20" t="n">
-        <v>4357725689750</v>
+        <v>4357847234250</v>
       </c>
       <c r="P20" t="n">
         <v>374500</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>삼성전자 주가 부진에 대한 부정적 의견 및 하이닉스와의 비교. 노조 및 경영진 관련 언급.</t>
+          <t>삼성전자, 영업이익 1위에도 불구하고 하이닉스 대비 낮은 주가 상승률에 대한 불만 제기. 노조, 이재용 관련 부정적 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['삼성전자', '하이닉스', '주가']</t>
+          <t>['영업이익', '노조', '주가']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2326,13 +2326,13 @@
         <v>0.52</v>
       </c>
       <c r="E21" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F21" t="n">
         <v>57</v>
       </c>
       <c r="G21" t="n">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="H21" t="n">
         <v>2.08</v>
@@ -2358,7 +2358,7 @@
         <v>1.56</v>
       </c>
       <c r="O21" t="n">
-        <v>72177549183</v>
+        <v>72217826348</v>
       </c>
       <c r="P21" t="n">
         <v>4335</v>
@@ -2418,13 +2418,13 @@
         <v>0.1</v>
       </c>
       <c r="E22" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F22" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G22" t="n">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="H22" t="n">
         <v>52.55</v>
@@ -2450,7 +2450,7 @@
         <v>21.01</v>
       </c>
       <c r="O22" t="n">
-        <v>89776303900</v>
+        <v>89776877650</v>
       </c>
       <c r="P22" t="n">
         <v>69500</v>
@@ -2510,13 +2510,13 @@
         <v>0.32</v>
       </c>
       <c r="E23" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F23" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G23" t="n">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="H23" t="n">
         <v>0.9399999999999999</v>
@@ -2542,7 +2542,7 @@
         <v>0.62</v>
       </c>
       <c r="O23" t="n">
-        <v>153244503025</v>
+        <v>153308352725</v>
       </c>
       <c r="P23" t="n">
         <v>15960</v>
@@ -2602,13 +2602,13 @@
         <v>0.38</v>
       </c>
       <c r="E24" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F24" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G24" t="n">
-        <v>779</v>
+        <v>811</v>
       </c>
       <c r="H24" t="n">
         <v>10.85</v>
@@ -2634,7 +2634,7 @@
         <v>10.47</v>
       </c>
       <c r="O24" t="n">
-        <v>296687153790</v>
+        <v>296793564740</v>
       </c>
       <c r="P24" t="n">
         <v>40350</v>
@@ -2650,16 +2650,16 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>원전 관련주 상승 및 대우건설 적정가 논의. 계약 체결 공시 언급.</t>
+          <t>대우건설, 미국 원전 참여 기대감 속 계약 체결 공시 발표. 공매도 세력 및 단기 투자에 대한 언급.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['원전', '계약', '적정가']</t>
+          <t>['원전', '공시', '계약체결']</t>
         </is>
       </c>
       <c r="X24" t="n">
